--- a/src-tauri/samples/mame/04_mame_custom_barcodes.xlsx
+++ b/src-tauri/samples/mame/04_mame_custom_barcodes.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>isps_f_1</t>
+          <t>egfp_f_1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -443,7 +443,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>isps_f_2</t>
+          <t>egfp_f_2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -455,7 +455,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>isps_f_3</t>
+          <t>egfp_f_3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -467,7 +467,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>isps_f_4</t>
+          <t>egfp_f_4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>isps_f_5</t>
+          <t>egfp_f_5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>isps_f_6</t>
+          <t>egfp_f_6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>isps_f_7</t>
+          <t>egfp_f_7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>isps_f_8</t>
+          <t>egfp_f_8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>isps_f_9</t>
+          <t>egfp_f_9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -539,7 +539,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>isps_f_10</t>
+          <t>egfp_f_10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>isps_f_11</t>
+          <t>egfp_f_11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>isps_f_12</t>
+          <t>egfp_f_12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>isps_r_1</t>
+          <t>egfp_r_1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>isps_r_2</t>
+          <t>egfp_r_2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>isps_r_3</t>
+          <t>egfp_r_3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -611,7 +611,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>isps_r_4</t>
+          <t>egfp_r_4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>isps_r_5</t>
+          <t>egfp_r_5</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>isps_r_6</t>
+          <t>egfp_r_6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>isps_r_7</t>
+          <t>egfp_r_7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>isps_r_8</t>
+          <t>egfp_r_8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">

--- a/src-tauri/samples/mame/04_mame_custom_barcodes.xlsx
+++ b/src-tauri/samples/mame/04_mame_custom_barcodes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="barcodes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="barcodes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AAGAAAGTTGTCGGTGTCTTTGTG</t>
+          <t>TATCTGACCTTCTATTCAGGGCGCGGTGG</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TCGATTCCGTTTGTAGTCGTCTGT</t>
+          <t>GCATACGTAACCTATTCAGGGCGCGGTGG</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GAGTCTTGTGTCCCAGTTACCAGG</t>
+          <t>AACTTGCATAGCTATTCAGGGCGCGGTGG</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TTCGGATTCTATCGTGTTTCCCTA</t>
+          <t>TGACCTAAGGTCTATTCAGGGCGCGGTGG</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CTTGTCCAGGGTTTGTGTAACCTT</t>
+          <t>CCGTATATAACCTATTCAGGGCGCGGTGG</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TTCTCGCAAAGGCAGAAAGTAGTC</t>
+          <t>GTAACCTGCATCTATTCAGGGCGCGGTGG</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GTGTTACCGTGGGAATGAATCCTT</t>
+          <t>AAGCTTACCATCTATTCAGGGCGCGGTGG</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TTCAGGGAACAAACCAAGTTACGT</t>
+          <t>TTCCGGATCATCTATTCAGGGCGCGGTGG</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AACTAGGCACAGCGAGTCTTGGTT</t>
+          <t>CCATTAGCATGCTATTCAGGGCGCGGTGG</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AAGCGTTGAAACCTTTGTCCTCTC</t>
+          <t>GGTTAACCATGCTATTCAGGGCGCGGTGG</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GTTTCATCTATCGGAGGGAATGGA</t>
+          <t>AATCCGTTAGCCTATTCAGGGCGCGGTGG</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CAGGTAGAAAGAAGCAGAATCGGA</t>
+          <t>GAACATACGGTCTATTCAGGGCGCGGTGG</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ACGTAACTTGGTTTGTTCCCTGAA</t>
+          <t>CCCTATGACAGCTCGTACCGGGGGTGCAC</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AAGGATTCATTCCCACGGTAACAC</t>
+          <t>GCTATAGCCTTCTCGTACCGGGGGTGCAC</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GACTACTTTCTGCCTTTGCGAGAA</t>
+          <t>TTGCAATCGATCTCGTACCGGGGGTGCAC</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AAGGTTACACAAACCCTGGACAAG</t>
+          <t>CCAGTATCGGTCTCGTACCGGGGGTGCAC</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TAGGGAAACACGATAGAATCCGAA</t>
+          <t>GGTACCTAATGCTCGTACCGGGGGTGCAC</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CCTGGTAACTGGGACACAAGACTC</t>
+          <t>AAGCTATCGCTCTCGTACCGGGGGTGCAC</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACAGACGACTACAAACGGAATCGA</t>
+          <t>TTCCAGCTTAGCTCGTACCGGGGGTGCAC</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CACAAAGACACCGACAACTTTCTT</t>
+          <t>AGAGTGCGGCTCTCGTACCGGGGGTGCAC</t>
         </is>
       </c>
     </row>
